--- a/test_data/Orion_Stress_Demo/PN-ALPHA-01/30101/BU 03/HRM/pre LAM_HRM-2031-0160/Panel 7/Coupon front/2031-03-01_08-00-00_ENG_Orion_Stress_Demo_BU03_Coupon_Front_Summary.xlsx
+++ b/test_data/Orion_Stress_Demo/PN-ALPHA-01/30101/BU 03/HRM/pre LAM_HRM-2031-0160/Panel 7/Coupon front/2031-03-01_08-00-00_ENG_Orion_Stress_Demo_BU03_Coupon_Front_Summary.xlsx
@@ -460,22 +460,22 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>16.98673</v>
+        <v>16.76514</v>
       </c>
       <c r="D2" t="n">
-        <v>16.78875</v>
+        <v>16.70057</v>
       </c>
       <c r="E2" t="n">
-        <v>16.76293</v>
+        <v>16.74732</v>
       </c>
       <c r="F2" t="n">
-        <v>42.66764</v>
+        <v>42.16411</v>
       </c>
       <c r="G2" t="n">
-        <v>0.04975</v>
+        <v>0.05142</v>
       </c>
       <c r="H2" t="n">
-        <v>1.80985</v>
+        <v>1.80478</v>
       </c>
     </row>
     <row r="3">
@@ -485,22 +485,22 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>16.91475</v>
+        <v>16.96188</v>
       </c>
       <c r="D3" t="n">
-        <v>16.41004</v>
+        <v>16.71842</v>
       </c>
       <c r="E3" t="n">
-        <v>16.6743</v>
+        <v>16.93305</v>
       </c>
       <c r="F3" t="n">
-        <v>42.39491</v>
+        <v>43.48209</v>
       </c>
       <c r="G3" t="n">
-        <v>0.05047</v>
+        <v>0.05113</v>
       </c>
       <c r="H3" t="n">
-        <v>1.85183</v>
+        <v>1.85472</v>
       </c>
     </row>
     <row r="4">
@@ -510,22 +510,22 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>16.8408</v>
+        <v>16.83286</v>
       </c>
       <c r="D4" t="n">
-        <v>16.66399</v>
+        <v>16.67152</v>
       </c>
       <c r="E4" t="n">
-        <v>16.95932</v>
+        <v>16.82471</v>
       </c>
       <c r="F4" t="n">
-        <v>43.18783</v>
+        <v>42.25978</v>
       </c>
       <c r="G4" t="n">
-        <v>0.05115</v>
+        <v>0.0502</v>
       </c>
       <c r="H4" t="n">
-        <v>1.76813</v>
+        <v>1.79635</v>
       </c>
     </row>
     <row r="5">
@@ -567,19 +567,19 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>16.65234</v>
+        <v>16.61032</v>
       </c>
       <c r="D6" t="n">
-        <v>16.08413</v>
+        <v>16.13742</v>
       </c>
       <c r="E6" t="n">
-        <v>16.56715</v>
+        <v>16.56154</v>
       </c>
       <c r="F6" t="n">
-        <v>22.06774</v>
+        <v>21.84306</v>
       </c>
       <c r="G6" t="n">
-        <v>34.18808</v>
+        <v>34.50319</v>
       </c>
     </row>
     <row r="7">
@@ -589,19 +589,19 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>16.54892</v>
+        <v>16.83182</v>
       </c>
       <c r="D7" t="n">
-        <v>16.36331</v>
+        <v>16.11044</v>
       </c>
       <c r="E7" t="n">
-        <v>16.59364</v>
+        <v>16.68884</v>
       </c>
       <c r="F7" t="n">
-        <v>21.41318</v>
+        <v>21.57628</v>
       </c>
       <c r="G7" t="n">
-        <v>34.15684</v>
+        <v>34.09875</v>
       </c>
     </row>
     <row r="8">
@@ -611,19 +611,19 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>17.07755</v>
+        <v>16.85859</v>
       </c>
       <c r="D8" t="n">
-        <v>16.04441</v>
+        <v>16.18297</v>
       </c>
       <c r="E8" t="n">
-        <v>16.67064</v>
+        <v>16.61686</v>
       </c>
       <c r="F8" t="n">
-        <v>21.74172</v>
+        <v>21.70807</v>
       </c>
       <c r="G8" t="n">
-        <v>33.92185</v>
+        <v>33.95851</v>
       </c>
     </row>
   </sheetData>
